--- a/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -408,6 +408,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -502,77 +520,157 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품목코드
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품목코드
 • 직접 입력 — 내부 자재 관리 코드
 • 예: BP-001, PIN-T450
 • 출하관리와 연계 검색 키</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 규격 (Specification)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 규격 (Specification)
 • 직접 입력 (좌측 정렬)
 • 제품 치수·전압·재질 등
 • 예: 10×10×5mm, 24V, SUS304</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단위
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단위
 • 드롭다운: EA / SET / M / KG / BOX / ROLL / PAIR / 기타
 • 수량의 단위</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메이커 (제조사)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메이커 (제조사)
 • 제조사 이름 입력
 • 예: KEYENCE, OMRON, SMC, 자체제작</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 카테고리
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 카테고리
 • 드롭다운: 지그부품 / 검사핀 / 커넥터 / 케이블 / 기타
 • 소모품 분류 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 등록일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 등록일
 • sync 실행 시 자동 입력 (수동 수정 불가)</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -587,280 +685,731 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
-• 영업단계 '수주확정' 이상일 때 자동 채번
-• 추가 PO는 기존 관리코드 유지 (행 여러 개 가능)</t>
+🟢 [신규 프로젝트]
+  비워두고 영업단계='수주확정' 입력 후 .bat 실행
+  → 자동 채번
+🟠 [추가 PO — 기존 검사기 추가 발주]
+  사용자가 기존 코드 직접 입력 (예: 005T2604)
+  → .bat 실행 시 그대로 유지 (재채번 X)
+⚠️ 같은 관리코드를 여러 행에 둘 때:
+  진척률·진행상태는 행마다 별도 관리되나
+  부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
+  → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
-• 포맷: [사업부]-[수주일 YYMMDD]  예: T-260401
-• 동일 수주일 복수 건: 뒤에 -N  예: T-260401-2
-• 관리코드 채번 직후 자동 생성 (수정 불가)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
+• 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
+• 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
+• 관리코드가 채번된 후 자동 생성
+  - C17 수주일이 비어있으면 오늘 날짜로 부여
+  - 정확한 수주일 입력 후 .bat 실행 권장
+• R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 규격 (Specification)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 규격 (Specification)
 • 직접 입력 (좌측 정렬)
 • 제품 치수·전압·재질 등
 • 예: 10×10×5mm, 24V, SUS304</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메이커 (제조사)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메이커 (제조사)
 • 제조사 이름 입력
 • 예: KEYENCE, OMRON, SMC, 자체제작</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 업체명
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 업체명 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단위
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단위
 • 드롭다운: EA / SET / M / KG / BOX / ROLL / PAIR / 기타
 • 수량의 단위</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 원산지
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 원산지 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ HS CODE
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ HS CODE (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발주일
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 발주일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고상태
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고일
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입고일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ INV번호
-(출하코드)
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ INV번호
+(출하코드) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하차수
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하차수 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 거래유형
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 거래유형 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관구분
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통관구분 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관분류
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통관분류 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 환율
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 환율 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상승률(%)
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 상승률(%) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하일
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하상태
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ DUTY(%)
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ DUTY(%) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ VAT(%)
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ VAT(%) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관세(KRW)
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관세(KRW) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AG4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관세(USD)
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관세(USD) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AH4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOX번호
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOX번호 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AI4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="AJ4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 무게(Kg)
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 무게(Kg) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AK4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PALLET SIZE
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PALLET SIZE (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AL4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관상태
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="AM4" authorId="0" shapeId="0">
       <text>
-        <t>▣ VN입고일
-(직접 입력)</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ VN입고일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AN4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1157,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1173,7 +1722,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 소모품목록 │ 2026</t>
         </is>
@@ -1189,7 +1738,7 @@
       <c r="J1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하대장 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1202,9 +1751,9 @@
       <c r="G2" s="22" t="n"/>
       <c r="H2" s="22" t="n"/>
       <c r="I2" s="23" t="n"/>
-      <c r="J2" s="64" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 00:25</t>
+      <c r="J2" s="70" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:34</t>
         </is>
       </c>
     </row>
@@ -1433,6 +1982,246 @@
       <c r="I14" s="30" t="n"/>
       <c r="J14" s="8" t="n"/>
     </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="43" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="29" t="n"/>
+      <c r="J15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="44" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="30" t="n"/>
+      <c r="J16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="43" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="29" t="n"/>
+      <c r="J17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="30" t="n"/>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="44" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="30" t="n"/>
+      <c r="J18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="43" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="29" t="n"/>
+      <c r="J19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="44" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="30" t="n"/>
+      <c r="J20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="43" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="29" t="n"/>
+      <c r="J21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="30" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="44" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="30" t="n"/>
+      <c r="J22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="43" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="29" t="n"/>
+      <c r="J23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="44" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="30" t="n"/>
+      <c r="J24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="43" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="29" t="n"/>
+      <c r="J25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="44" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="30" t="n"/>
+      <c r="J26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="43" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="29" t="n"/>
+      <c r="J27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="30" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="44" t="n"/>
+      <c r="H28" s="9" t="n"/>
+      <c r="I28" s="30" t="n"/>
+      <c r="J28" s="8" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="29" t="n"/>
+      <c r="G29" s="43" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="29" t="n"/>
+      <c r="J29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="30" t="n"/>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="44" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="30" t="n"/>
+      <c r="J30" s="8" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="43" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="29" t="n"/>
+      <c r="J31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="30" t="n"/>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="44" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="30" t="n"/>
+      <c r="J32" s="8" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="29" t="n"/>
+      <c r="G33" s="43" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="29" t="n"/>
+      <c r="J33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="44" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="30" t="n"/>
+      <c r="J34" s="8" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
@@ -1440,10 +2229,10 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="E5:E34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"EA,SET,M,KG,BOX,ROLL,PAIR,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="H5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"지그부품,검사핀,커넥터,케이블,기타"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1459,7 +2248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="61" min="1" max="1"/>
@@ -1505,7 +2294,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 출하관리 │ 2026</t>
         </is>
@@ -1551,7 +2340,7 @@
       <c r="AN1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하관리  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1594,9 +2383,9 @@
       <c r="AK2" s="22" t="n"/>
       <c r="AL2" s="22" t="n"/>
       <c r="AM2" s="23" t="n"/>
-      <c r="AN2" s="64" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 00:25</t>
+      <c r="AN2" s="70" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:34</t>
         </is>
       </c>
     </row>
@@ -2429,6 +3218,846 @@
       <c r="AM14" s="9" t="n"/>
       <c r="AN14" s="30" t="n"/>
     </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="43" t="n"/>
+      <c r="L15" s="45" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="6" t="n"/>
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="n"/>
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
+      <c r="AA15" s="6" t="n"/>
+      <c r="AB15" s="45" t="n"/>
+      <c r="AC15" s="45" t="n"/>
+      <c r="AD15" s="45" t="n"/>
+      <c r="AE15" s="45" t="n"/>
+      <c r="AF15" s="45" t="n"/>
+      <c r="AG15" s="45" t="n"/>
+      <c r="AH15" s="6" t="n"/>
+      <c r="AI15" s="38" t="n"/>
+      <c r="AJ15" s="6" t="n"/>
+      <c r="AK15" s="6" t="n"/>
+      <c r="AL15" s="6" t="n"/>
+      <c r="AM15" s="6" t="n"/>
+      <c r="AN15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="30" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="39" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="44" t="n"/>
+      <c r="L16" s="46" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="9" t="n"/>
+      <c r="S16" s="9" t="n"/>
+      <c r="T16" s="9" t="n"/>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="9" t="n"/>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="46" t="n"/>
+      <c r="AC16" s="46" t="n"/>
+      <c r="AD16" s="46" t="n"/>
+      <c r="AE16" s="46" t="n"/>
+      <c r="AF16" s="46" t="n"/>
+      <c r="AG16" s="46" t="n"/>
+      <c r="AH16" s="9" t="n"/>
+      <c r="AI16" s="39" t="n"/>
+      <c r="AJ16" s="9" t="n"/>
+      <c r="AK16" s="9" t="n"/>
+      <c r="AL16" s="9" t="n"/>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="43" t="n"/>
+      <c r="L17" s="45" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
+      <c r="T17" s="6" t="n"/>
+      <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
+      <c r="Z17" s="6" t="n"/>
+      <c r="AA17" s="6" t="n"/>
+      <c r="AB17" s="45" t="n"/>
+      <c r="AC17" s="45" t="n"/>
+      <c r="AD17" s="45" t="n"/>
+      <c r="AE17" s="45" t="n"/>
+      <c r="AF17" s="45" t="n"/>
+      <c r="AG17" s="45" t="n"/>
+      <c r="AH17" s="6" t="n"/>
+      <c r="AI17" s="38" t="n"/>
+      <c r="AJ17" s="6" t="n"/>
+      <c r="AK17" s="6" t="n"/>
+      <c r="AL17" s="6" t="n"/>
+      <c r="AM17" s="6" t="n"/>
+      <c r="AN17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="30" t="n"/>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="30" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="39" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="44" t="n"/>
+      <c r="L18" s="46" t="n"/>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="9" t="n"/>
+      <c r="T18" s="9" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="9" t="n"/>
+      <c r="W18" s="9" t="n"/>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="9" t="n"/>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="46" t="n"/>
+      <c r="AC18" s="46" t="n"/>
+      <c r="AD18" s="46" t="n"/>
+      <c r="AE18" s="46" t="n"/>
+      <c r="AF18" s="46" t="n"/>
+      <c r="AG18" s="46" t="n"/>
+      <c r="AH18" s="9" t="n"/>
+      <c r="AI18" s="39" t="n"/>
+      <c r="AJ18" s="9" t="n"/>
+      <c r="AK18" s="9" t="n"/>
+      <c r="AL18" s="9" t="n"/>
+      <c r="AM18" s="9" t="n"/>
+      <c r="AN18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="43" t="n"/>
+      <c r="L19" s="45" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
+      <c r="T19" s="6" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
+      <c r="Z19" s="6" t="n"/>
+      <c r="AA19" s="6" t="n"/>
+      <c r="AB19" s="45" t="n"/>
+      <c r="AC19" s="45" t="n"/>
+      <c r="AD19" s="45" t="n"/>
+      <c r="AE19" s="45" t="n"/>
+      <c r="AF19" s="45" t="n"/>
+      <c r="AG19" s="45" t="n"/>
+      <c r="AH19" s="6" t="n"/>
+      <c r="AI19" s="38" t="n"/>
+      <c r="AJ19" s="6" t="n"/>
+      <c r="AK19" s="6" t="n"/>
+      <c r="AL19" s="6" t="n"/>
+      <c r="AM19" s="6" t="n"/>
+      <c r="AN19" s="29" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="30" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="39" t="n"/>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="44" t="n"/>
+      <c r="L20" s="46" t="n"/>
+      <c r="M20" s="9" t="n"/>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="9" t="n"/>
+      <c r="S20" s="9" t="n"/>
+      <c r="T20" s="9" t="n"/>
+      <c r="U20" s="9" t="n"/>
+      <c r="V20" s="9" t="n"/>
+      <c r="W20" s="9" t="n"/>
+      <c r="X20" s="9" t="n"/>
+      <c r="Y20" s="9" t="n"/>
+      <c r="Z20" s="9" t="n"/>
+      <c r="AA20" s="9" t="n"/>
+      <c r="AB20" s="46" t="n"/>
+      <c r="AC20" s="46" t="n"/>
+      <c r="AD20" s="46" t="n"/>
+      <c r="AE20" s="46" t="n"/>
+      <c r="AF20" s="46" t="n"/>
+      <c r="AG20" s="46" t="n"/>
+      <c r="AH20" s="9" t="n"/>
+      <c r="AI20" s="39" t="n"/>
+      <c r="AJ20" s="9" t="n"/>
+      <c r="AK20" s="9" t="n"/>
+      <c r="AL20" s="9" t="n"/>
+      <c r="AM20" s="9" t="n"/>
+      <c r="AN20" s="30" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="43" t="n"/>
+      <c r="L21" s="45" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="n"/>
+      <c r="T21" s="6" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
+      <c r="Z21" s="6" t="n"/>
+      <c r="AA21" s="6" t="n"/>
+      <c r="AB21" s="45" t="n"/>
+      <c r="AC21" s="45" t="n"/>
+      <c r="AD21" s="45" t="n"/>
+      <c r="AE21" s="45" t="n"/>
+      <c r="AF21" s="45" t="n"/>
+      <c r="AG21" s="45" t="n"/>
+      <c r="AH21" s="6" t="n"/>
+      <c r="AI21" s="38" t="n"/>
+      <c r="AJ21" s="6" t="n"/>
+      <c r="AK21" s="6" t="n"/>
+      <c r="AL21" s="6" t="n"/>
+      <c r="AM21" s="6" t="n"/>
+      <c r="AN21" s="29" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="30" t="n"/>
+      <c r="E22" s="30" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="39" t="n"/>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="44" t="n"/>
+      <c r="L22" s="46" t="n"/>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="9" t="n"/>
+      <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="9" t="n"/>
+      <c r="S22" s="9" t="n"/>
+      <c r="T22" s="9" t="n"/>
+      <c r="U22" s="9" t="n"/>
+      <c r="V22" s="9" t="n"/>
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="9" t="n"/>
+      <c r="Y22" s="9" t="n"/>
+      <c r="Z22" s="9" t="n"/>
+      <c r="AA22" s="9" t="n"/>
+      <c r="AB22" s="46" t="n"/>
+      <c r="AC22" s="46" t="n"/>
+      <c r="AD22" s="46" t="n"/>
+      <c r="AE22" s="46" t="n"/>
+      <c r="AF22" s="46" t="n"/>
+      <c r="AG22" s="46" t="n"/>
+      <c r="AH22" s="9" t="n"/>
+      <c r="AI22" s="39" t="n"/>
+      <c r="AJ22" s="9" t="n"/>
+      <c r="AK22" s="9" t="n"/>
+      <c r="AL22" s="9" t="n"/>
+      <c r="AM22" s="9" t="n"/>
+      <c r="AN22" s="30" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="38" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="43" t="n"/>
+      <c r="L23" s="45" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="6" t="n"/>
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="n"/>
+      <c r="T23" s="6" t="n"/>
+      <c r="U23" s="6" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
+      <c r="X23" s="6" t="n"/>
+      <c r="Y23" s="6" t="n"/>
+      <c r="Z23" s="6" t="n"/>
+      <c r="AA23" s="6" t="n"/>
+      <c r="AB23" s="45" t="n"/>
+      <c r="AC23" s="45" t="n"/>
+      <c r="AD23" s="45" t="n"/>
+      <c r="AE23" s="45" t="n"/>
+      <c r="AF23" s="45" t="n"/>
+      <c r="AG23" s="45" t="n"/>
+      <c r="AH23" s="6" t="n"/>
+      <c r="AI23" s="38" t="n"/>
+      <c r="AJ23" s="6" t="n"/>
+      <c r="AK23" s="6" t="n"/>
+      <c r="AL23" s="6" t="n"/>
+      <c r="AM23" s="6" t="n"/>
+      <c r="AN23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="39" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="44" t="n"/>
+      <c r="L24" s="46" t="n"/>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="9" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="9" t="n"/>
+      <c r="Z24" s="9" t="n"/>
+      <c r="AA24" s="9" t="n"/>
+      <c r="AB24" s="46" t="n"/>
+      <c r="AC24" s="46" t="n"/>
+      <c r="AD24" s="46" t="n"/>
+      <c r="AE24" s="46" t="n"/>
+      <c r="AF24" s="46" t="n"/>
+      <c r="AG24" s="46" t="n"/>
+      <c r="AH24" s="9" t="n"/>
+      <c r="AI24" s="39" t="n"/>
+      <c r="AJ24" s="9" t="n"/>
+      <c r="AK24" s="9" t="n"/>
+      <c r="AL24" s="9" t="n"/>
+      <c r="AM24" s="9" t="n"/>
+      <c r="AN24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="38" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="43" t="n"/>
+      <c r="L25" s="45" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="6" t="n"/>
+      <c r="R25" s="6" t="n"/>
+      <c r="S25" s="6" t="n"/>
+      <c r="T25" s="6" t="n"/>
+      <c r="U25" s="6" t="n"/>
+      <c r="V25" s="6" t="n"/>
+      <c r="W25" s="6" t="n"/>
+      <c r="X25" s="6" t="n"/>
+      <c r="Y25" s="6" t="n"/>
+      <c r="Z25" s="6" t="n"/>
+      <c r="AA25" s="6" t="n"/>
+      <c r="AB25" s="45" t="n"/>
+      <c r="AC25" s="45" t="n"/>
+      <c r="AD25" s="45" t="n"/>
+      <c r="AE25" s="45" t="n"/>
+      <c r="AF25" s="45" t="n"/>
+      <c r="AG25" s="45" t="n"/>
+      <c r="AH25" s="6" t="n"/>
+      <c r="AI25" s="38" t="n"/>
+      <c r="AJ25" s="6" t="n"/>
+      <c r="AK25" s="6" t="n"/>
+      <c r="AL25" s="6" t="n"/>
+      <c r="AM25" s="6" t="n"/>
+      <c r="AN25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="39" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="44" t="n"/>
+      <c r="L26" s="46" t="n"/>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="9" t="n"/>
+      <c r="S26" s="9" t="n"/>
+      <c r="T26" s="9" t="n"/>
+      <c r="U26" s="9" t="n"/>
+      <c r="V26" s="9" t="n"/>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="9" t="n"/>
+      <c r="Y26" s="9" t="n"/>
+      <c r="Z26" s="9" t="n"/>
+      <c r="AA26" s="9" t="n"/>
+      <c r="AB26" s="46" t="n"/>
+      <c r="AC26" s="46" t="n"/>
+      <c r="AD26" s="46" t="n"/>
+      <c r="AE26" s="46" t="n"/>
+      <c r="AF26" s="46" t="n"/>
+      <c r="AG26" s="46" t="n"/>
+      <c r="AH26" s="9" t="n"/>
+      <c r="AI26" s="39" t="n"/>
+      <c r="AJ26" s="9" t="n"/>
+      <c r="AK26" s="9" t="n"/>
+      <c r="AL26" s="9" t="n"/>
+      <c r="AM26" s="9" t="n"/>
+      <c r="AN26" s="30" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="38" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="43" t="n"/>
+      <c r="L27" s="45" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n"/>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n"/>
+      <c r="Q27" s="6" t="n"/>
+      <c r="R27" s="6" t="n"/>
+      <c r="S27" s="6" t="n"/>
+      <c r="T27" s="6" t="n"/>
+      <c r="U27" s="6" t="n"/>
+      <c r="V27" s="6" t="n"/>
+      <c r="W27" s="6" t="n"/>
+      <c r="X27" s="6" t="n"/>
+      <c r="Y27" s="6" t="n"/>
+      <c r="Z27" s="6" t="n"/>
+      <c r="AA27" s="6" t="n"/>
+      <c r="AB27" s="45" t="n"/>
+      <c r="AC27" s="45" t="n"/>
+      <c r="AD27" s="45" t="n"/>
+      <c r="AE27" s="45" t="n"/>
+      <c r="AF27" s="45" t="n"/>
+      <c r="AG27" s="45" t="n"/>
+      <c r="AH27" s="6" t="n"/>
+      <c r="AI27" s="38" t="n"/>
+      <c r="AJ27" s="6" t="n"/>
+      <c r="AK27" s="6" t="n"/>
+      <c r="AL27" s="6" t="n"/>
+      <c r="AM27" s="6" t="n"/>
+      <c r="AN27" s="29" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="30" t="n"/>
+      <c r="E28" s="30" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="n"/>
+      <c r="I28" s="39" t="n"/>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="44" t="n"/>
+      <c r="L28" s="46" t="n"/>
+      <c r="M28" s="9" t="n"/>
+      <c r="N28" s="9" t="n"/>
+      <c r="O28" s="9" t="n"/>
+      <c r="P28" s="9" t="n"/>
+      <c r="Q28" s="9" t="n"/>
+      <c r="R28" s="9" t="n"/>
+      <c r="S28" s="9" t="n"/>
+      <c r="T28" s="9" t="n"/>
+      <c r="U28" s="9" t="n"/>
+      <c r="V28" s="9" t="n"/>
+      <c r="W28" s="9" t="n"/>
+      <c r="X28" s="9" t="n"/>
+      <c r="Y28" s="9" t="n"/>
+      <c r="Z28" s="9" t="n"/>
+      <c r="AA28" s="9" t="n"/>
+      <c r="AB28" s="46" t="n"/>
+      <c r="AC28" s="46" t="n"/>
+      <c r="AD28" s="46" t="n"/>
+      <c r="AE28" s="46" t="n"/>
+      <c r="AF28" s="46" t="n"/>
+      <c r="AG28" s="46" t="n"/>
+      <c r="AH28" s="9" t="n"/>
+      <c r="AI28" s="39" t="n"/>
+      <c r="AJ28" s="9" t="n"/>
+      <c r="AK28" s="9" t="n"/>
+      <c r="AL28" s="9" t="n"/>
+      <c r="AM28" s="9" t="n"/>
+      <c r="AN28" s="30" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="29" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="38" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="43" t="n"/>
+      <c r="L29" s="45" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n"/>
+      <c r="Q29" s="6" t="n"/>
+      <c r="R29" s="6" t="n"/>
+      <c r="S29" s="6" t="n"/>
+      <c r="T29" s="6" t="n"/>
+      <c r="U29" s="6" t="n"/>
+      <c r="V29" s="6" t="n"/>
+      <c r="W29" s="6" t="n"/>
+      <c r="X29" s="6" t="n"/>
+      <c r="Y29" s="6" t="n"/>
+      <c r="Z29" s="6" t="n"/>
+      <c r="AA29" s="6" t="n"/>
+      <c r="AB29" s="45" t="n"/>
+      <c r="AC29" s="45" t="n"/>
+      <c r="AD29" s="45" t="n"/>
+      <c r="AE29" s="45" t="n"/>
+      <c r="AF29" s="45" t="n"/>
+      <c r="AG29" s="45" t="n"/>
+      <c r="AH29" s="6" t="n"/>
+      <c r="AI29" s="38" t="n"/>
+      <c r="AJ29" s="6" t="n"/>
+      <c r="AK29" s="6" t="n"/>
+      <c r="AL29" s="6" t="n"/>
+      <c r="AM29" s="6" t="n"/>
+      <c r="AN29" s="29" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="30" t="n"/>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="30" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="39" t="n"/>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="44" t="n"/>
+      <c r="L30" s="46" t="n"/>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="9" t="n"/>
+      <c r="Q30" s="9" t="n"/>
+      <c r="R30" s="9" t="n"/>
+      <c r="S30" s="9" t="n"/>
+      <c r="T30" s="9" t="n"/>
+      <c r="U30" s="9" t="n"/>
+      <c r="V30" s="9" t="n"/>
+      <c r="W30" s="9" t="n"/>
+      <c r="X30" s="9" t="n"/>
+      <c r="Y30" s="9" t="n"/>
+      <c r="Z30" s="9" t="n"/>
+      <c r="AA30" s="9" t="n"/>
+      <c r="AB30" s="46" t="n"/>
+      <c r="AC30" s="46" t="n"/>
+      <c r="AD30" s="46" t="n"/>
+      <c r="AE30" s="46" t="n"/>
+      <c r="AF30" s="46" t="n"/>
+      <c r="AG30" s="46" t="n"/>
+      <c r="AH30" s="9" t="n"/>
+      <c r="AI30" s="39" t="n"/>
+      <c r="AJ30" s="9" t="n"/>
+      <c r="AK30" s="9" t="n"/>
+      <c r="AL30" s="9" t="n"/>
+      <c r="AM30" s="9" t="n"/>
+      <c r="AN30" s="30" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="38" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="43" t="n"/>
+      <c r="L31" s="45" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="6" t="n"/>
+      <c r="Q31" s="6" t="n"/>
+      <c r="R31" s="6" t="n"/>
+      <c r="S31" s="6" t="n"/>
+      <c r="T31" s="6" t="n"/>
+      <c r="U31" s="6" t="n"/>
+      <c r="V31" s="6" t="n"/>
+      <c r="W31" s="6" t="n"/>
+      <c r="X31" s="6" t="n"/>
+      <c r="Y31" s="6" t="n"/>
+      <c r="Z31" s="6" t="n"/>
+      <c r="AA31" s="6" t="n"/>
+      <c r="AB31" s="45" t="n"/>
+      <c r="AC31" s="45" t="n"/>
+      <c r="AD31" s="45" t="n"/>
+      <c r="AE31" s="45" t="n"/>
+      <c r="AF31" s="45" t="n"/>
+      <c r="AG31" s="45" t="n"/>
+      <c r="AH31" s="6" t="n"/>
+      <c r="AI31" s="38" t="n"/>
+      <c r="AJ31" s="6" t="n"/>
+      <c r="AK31" s="6" t="n"/>
+      <c r="AL31" s="6" t="n"/>
+      <c r="AM31" s="6" t="n"/>
+      <c r="AN31" s="29" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="30" t="n"/>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="30" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="39" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="44" t="n"/>
+      <c r="L32" s="46" t="n"/>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="9" t="n"/>
+      <c r="Q32" s="9" t="n"/>
+      <c r="R32" s="9" t="n"/>
+      <c r="S32" s="9" t="n"/>
+      <c r="T32" s="9" t="n"/>
+      <c r="U32" s="9" t="n"/>
+      <c r="V32" s="9" t="n"/>
+      <c r="W32" s="9" t="n"/>
+      <c r="X32" s="9" t="n"/>
+      <c r="Y32" s="9" t="n"/>
+      <c r="Z32" s="9" t="n"/>
+      <c r="AA32" s="9" t="n"/>
+      <c r="AB32" s="46" t="n"/>
+      <c r="AC32" s="46" t="n"/>
+      <c r="AD32" s="46" t="n"/>
+      <c r="AE32" s="46" t="n"/>
+      <c r="AF32" s="46" t="n"/>
+      <c r="AG32" s="46" t="n"/>
+      <c r="AH32" s="9" t="n"/>
+      <c r="AI32" s="39" t="n"/>
+      <c r="AJ32" s="9" t="n"/>
+      <c r="AK32" s="9" t="n"/>
+      <c r="AL32" s="9" t="n"/>
+      <c r="AM32" s="9" t="n"/>
+      <c r="AN32" s="30" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="29" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="38" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="43" t="n"/>
+      <c r="L33" s="45" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="n"/>
+      <c r="Q33" s="6" t="n"/>
+      <c r="R33" s="6" t="n"/>
+      <c r="S33" s="6" t="n"/>
+      <c r="T33" s="6" t="n"/>
+      <c r="U33" s="6" t="n"/>
+      <c r="V33" s="6" t="n"/>
+      <c r="W33" s="6" t="n"/>
+      <c r="X33" s="6" t="n"/>
+      <c r="Y33" s="6" t="n"/>
+      <c r="Z33" s="6" t="n"/>
+      <c r="AA33" s="6" t="n"/>
+      <c r="AB33" s="45" t="n"/>
+      <c r="AC33" s="45" t="n"/>
+      <c r="AD33" s="45" t="n"/>
+      <c r="AE33" s="45" t="n"/>
+      <c r="AF33" s="45" t="n"/>
+      <c r="AG33" s="45" t="n"/>
+      <c r="AH33" s="6" t="n"/>
+      <c r="AI33" s="38" t="n"/>
+      <c r="AJ33" s="6" t="n"/>
+      <c r="AK33" s="6" t="n"/>
+      <c r="AL33" s="6" t="n"/>
+      <c r="AM33" s="6" t="n"/>
+      <c r="AN33" s="29" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="39" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="44" t="n"/>
+      <c r="L34" s="46" t="n"/>
+      <c r="M34" s="9" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="9" t="n"/>
+      <c r="S34" s="9" t="n"/>
+      <c r="T34" s="9" t="n"/>
+      <c r="U34" s="9" t="n"/>
+      <c r="V34" s="9" t="n"/>
+      <c r="W34" s="9" t="n"/>
+      <c r="X34" s="9" t="n"/>
+      <c r="Y34" s="9" t="n"/>
+      <c r="Z34" s="9" t="n"/>
+      <c r="AA34" s="9" t="n"/>
+      <c r="AB34" s="46" t="n"/>
+      <c r="AC34" s="46" t="n"/>
+      <c r="AD34" s="46" t="n"/>
+      <c r="AE34" s="46" t="n"/>
+      <c r="AF34" s="46" t="n"/>
+      <c r="AG34" s="46" t="n"/>
+      <c r="AH34" s="9" t="n"/>
+      <c r="AI34" s="39" t="n"/>
+      <c r="AJ34" s="9" t="n"/>
+      <c r="AK34" s="9" t="n"/>
+      <c r="AL34" s="9" t="n"/>
+      <c r="AM34" s="9" t="n"/>
+      <c r="AN34" s="30" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
@@ -2436,31 +4065,31 @@
     <mergeCell ref="A1:AN1"/>
   </mergeCells>
   <dataValidations count="9">
-    <dataValidation sqref="J5:J14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="J5:J34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"KRW,USD"</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="O5:O34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"미입고,입고완료"</formula1>
     </dataValidation>
-    <dataValidation sqref="Y5:Y14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="Y5:Y34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"미출하,출하완료"</formula1>
     </dataValidation>
-    <dataValidation sqref="S5:S14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="S5:S34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"부품판매,위탁가공"</formula1>
     </dataValidation>
-    <dataValidation sqref="T5:T14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="T5:T34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"국내,수책통관,정식통관"</formula1>
     </dataValidation>
-    <dataValidation sqref="U5:U14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="U5:U34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"해상,항공,특송,핸드캐리,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="AL5:AL14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="AL5:AL34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"준비중,입고대기,포장완료,선적완료,통관중,통관완료,VN입고완료"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="G5:G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"EA,SET,M,KG,BOX,ROLL,PAIR,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
+    <dataValidation sqref="H5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"KOREA,JAPAN,CHINA,TAIWAN,USA,GERMANY,FRANCE,기타"</formula1>
     </dataValidation>
   </dataValidations>

--- a/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
@@ -143,7 +143,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -209,11 +209,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -436,6 +465,17 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1722,7 +1762,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="68" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 소모품목록 │ 2026</t>
         </is>
@@ -1738,7 +1778,7 @@
       <c r="J1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="69" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하대장 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1748,14 +1788,14 @@
       <c r="D2" s="22" t="n"/>
       <c r="E2" s="22" t="n"/>
       <c r="F2" s="22" t="n"/>
-      <c r="G2" s="22" t="n"/>
-      <c r="H2" s="22" t="n"/>
-      <c r="I2" s="23" t="n"/>
-      <c r="J2" s="70" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:34</t>
-        </is>
-      </c>
+      <c r="G2" s="23" t="n"/>
+      <c r="H2" s="73" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="I2" s="74" t="n"/>
+      <c r="J2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2224,9 +2264,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="H2:J2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E5:E34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
@@ -2294,7 +2335,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="68" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 출하관리 │ 2026</t>
         </is>
@@ -2340,7 +2381,7 @@
       <c r="AN1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="69" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하관리  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -2380,14 +2421,14 @@
       <c r="AH2" s="22" t="n"/>
       <c r="AI2" s="22" t="n"/>
       <c r="AJ2" s="22" t="n"/>
-      <c r="AK2" s="22" t="n"/>
-      <c r="AL2" s="22" t="n"/>
-      <c r="AM2" s="23" t="n"/>
-      <c r="AN2" s="70" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:34</t>
-        </is>
-      </c>
+      <c r="AK2" s="23" t="n"/>
+      <c r="AL2" s="73" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="AM2" s="74" t="n"/>
+      <c r="AN2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -4060,9 +4101,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:AM2"/>
+  <mergeCells count="3">
     <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
   </mergeCells>
   <dataValidations count="9">
     <dataValidation sqref="J5:J34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
@@ -242,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -476,6 +476,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -826,11 +835,16 @@
           </rPr>
           <t>▣ 업체명 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -860,11 +874,16 @@
           </rPr>
           <t>▣ 원산지 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -946,11 +965,16 @@
           </rPr>
           <t>▣ HS CODE (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -965,11 +989,16 @@
           </rPr>
           <t>▣ 발주일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1003,11 +1032,16 @@
           </rPr>
           <t>▣ 입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1020,14 +1054,18 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ INV번호
-(출하코드) (세부항목 진척률)
+          <t>▣ INV번호(출하코드) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1042,11 +1080,16 @@
           </rPr>
           <t>▣ 출하차수 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1061,11 +1104,16 @@
           </rPr>
           <t>▣ 거래유형 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1080,11 +1128,16 @@
           </rPr>
           <t>▣ 통관구분 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1099,11 +1152,16 @@
           </rPr>
           <t>▣ 통관분류 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1118,11 +1176,16 @@
           </rPr>
           <t>▣ 환율 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1137,11 +1200,16 @@
           </rPr>
           <t>▣ 상승률(%) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1156,11 +1224,16 @@
           </rPr>
           <t>▣ 출하일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1194,11 +1267,16 @@
           </rPr>
           <t>▣ DUTY(%) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1213,11 +1291,16 @@
           </rPr>
           <t>▣ VAT(%) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1298,11 +1381,16 @@
           </rPr>
           <t>▣ 관세(KRW) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1317,11 +1405,16 @@
           </rPr>
           <t>▣ 관세(USD) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1336,11 +1429,16 @@
           </rPr>
           <t>▣ BOX번호 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1371,11 +1469,16 @@
           </rPr>
           <t>▣ 무게(Kg) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1390,11 +1493,16 @@
           </rPr>
           <t>▣ PALLET SIZE (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1428,11 +1536,16 @@
           </rPr>
           <t>▣ VN입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1762,7 +1875,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="71" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 소모품목록 │ 2026</t>
         </is>
@@ -1778,7 +1891,7 @@
       <c r="J1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="72" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하대장 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1789,13 +1902,13 @@
       <c r="E2" s="22" t="n"/>
       <c r="F2" s="22" t="n"/>
       <c r="G2" s="23" t="n"/>
-      <c r="H2" s="73" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="I2" s="74" t="n"/>
-      <c r="J2" s="75" t="n"/>
+      <c r="H2" s="78" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:27</t>
+        </is>
+      </c>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="23" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2335,7 +2448,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="71" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 출하관리 │ 2026</t>
         </is>
@@ -2381,7 +2494,7 @@
       <c r="AN1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="72" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하관리  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -2422,13 +2535,13 @@
       <c r="AI2" s="22" t="n"/>
       <c r="AJ2" s="22" t="n"/>
       <c r="AK2" s="23" t="n"/>
-      <c r="AL2" s="73" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="AM2" s="74" t="n"/>
-      <c r="AN2" s="75" t="n"/>
+      <c r="AL2" s="78" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:27</t>
+        </is>
+      </c>
+      <c r="AM2" s="22" t="n"/>
+      <c r="AN2" s="23" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
@@ -242,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -476,6 +476,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1875,7 +1884,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 소모품목록 │ 2026</t>
         </is>
@@ -1891,7 +1900,7 @@
       <c r="J1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하대장 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1902,9 +1911,9 @@
       <c r="E2" s="22" t="n"/>
       <c r="F2" s="22" t="n"/>
       <c r="G2" s="23" t="n"/>
-      <c r="H2" s="78" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:27</t>
+      <c r="H2" s="81" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="I2" s="22" t="n"/>
@@ -2448,7 +2457,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 출하관리 │ 2026</t>
         </is>
@@ -2494,7 +2503,7 @@
       <c r="AN1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하관리  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -2535,9 +2544,9 @@
       <c r="AI2" s="22" t="n"/>
       <c r="AJ2" s="22" t="n"/>
       <c r="AK2" s="23" t="n"/>
-      <c r="AL2" s="78" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:27</t>
+      <c r="AL2" s="81" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="AM2" s="22" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/05_소모품/KNK_소모품_출하대장_2026.xlsx
@@ -242,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -476,6 +476,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1884,7 +1893,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 소모품목록 │ 2026</t>
         </is>
@@ -1900,7 +1909,7 @@
       <c r="J1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="80" t="inlineStr">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하대장 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1911,9 +1920,9 @@
       <c r="E2" s="22" t="n"/>
       <c r="F2" s="22" t="n"/>
       <c r="G2" s="23" t="n"/>
-      <c r="H2" s="81" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="H2" s="84" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:01</t>
         </is>
       </c>
       <c r="I2" s="22" t="n"/>
@@ -2457,7 +2466,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 소모품 │ 출하관리 │ 2026</t>
         </is>
@@ -2503,7 +2512,7 @@
       <c r="AN1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="80" t="inlineStr">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  소모품 출하관리  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -2544,9 +2553,9 @@
       <c r="AI2" s="22" t="n"/>
       <c r="AJ2" s="22" t="n"/>
       <c r="AK2" s="23" t="n"/>
-      <c r="AL2" s="81" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="AL2" s="84" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:01</t>
         </is>
       </c>
       <c r="AM2" s="22" t="n"/>
